--- a/output/laminas_comunales/comunal_o_ocup_a_2022_atacama.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2022_atacama.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>45.5108946346201</v>
+        <v>63.0442708333333</v>
       </c>
     </row>
     <row r="3">
@@ -399,112 +399,1237 @@
         </is>
       </c>
       <c r="C3">
-        <v>43.630239538524</v>
+        <v>61.6533298610289</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="C4">
-        <v>38.0383962596471</v>
+        <v>60.2887222842559</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="C5">
-        <v>37.9523445463812</v>
+        <v>60.0036941632221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huasco</t>
+          <t>Diego de Almagro</t>
         </is>
       </c>
       <c r="C6">
-        <v>37.9392189488108</v>
+        <v>59.6518792359827</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vallenar</t>
+          <t>Huasco</t>
         </is>
       </c>
       <c r="C7">
-        <v>37.4269249173029</v>
+        <v>58.7989323843416</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Freirina</t>
+          <t>Vallenar</t>
         </is>
       </c>
       <c r="C8">
-        <v>35.2459646425826</v>
+        <v>57.8645428645429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caldera</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="C9">
-        <v>33.3342589507201</v>
+        <v>57.4155533832953</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>57.2836821600072</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>56.5352879213483</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>55.2500618199802</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>55.026398292536</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>54.7048509643483</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>53.176687575433</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>52.0193456930817</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>51.4627961010994</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>51.4396358046589</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>50.9344088163049</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>50.8187569780424</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>50.3915819951002</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>3302</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Alto del Carmen</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="C22">
+        <v>49.9916998671979</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>48.801093303516</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>48.5977239287752</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>48.320673220137</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>47.8634212305612</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>47.3208498003053</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>46.7012744451769</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>46.2603346181778</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>45.9199489423778</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>45.5108946346201</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>45.289492494639</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>44.5819904287528</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>44.4109560067682</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>43.630239538524</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>42.201127981289</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>41.6788261997406</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>41.6007499853518</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>38.9442336074215</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>38.0383962596471</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>37.9523445463812</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>37.9392189488108</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>37.4269249173029</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>36.7580652950835</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>35.7943469785575</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>35.4783975069984</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>35.2459646425826</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>35.0171701173371</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>34.5475671270292</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>34.3325791855204</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>34.0124693832109</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>33.7012528991225</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>33.6359051941503</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>33.5134774486256</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>33.3342589507201</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>31.9594034797017</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>31.6948937333958</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>31.4796641587613</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>31.4411569148936</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>31.4013743381773</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>31.0460638039787</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>30.1470588235294</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>28.7143408129813</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>28.6921614198183</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>28.6451028517999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C66">
         <v>28.6319231072245</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>27.9935869192735</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>27.1351986487479</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>27.0882237871675</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>26.5863573269879</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>25.8351893095768</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>24.9407072013799</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>22.3981527296718</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>21.0330776605944</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>16.348014681348</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>15.797619047619</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>15.2651623345711</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>15.0322061191626</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>12.9884267216684</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>11.7747641509434</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>11.586368234699</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>10.9427083333333</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>10.880195599022</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>10.8198654166906</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>8.54651162790698</v>
       </c>
     </row>
   </sheetData>
